--- a/reports/devops-juniors-israel-2026-W41.xlsx
+++ b/reports/devops-juniors-israel-2026-W41.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-05T14:26:43</t>
+    <t xml:space="preserve">2026-10-06T13:14:31</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,6 +217,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -250,9 +265,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -346,19 +358,37 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator #1350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Terraform/IaC, Networking, Virtualization, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-stealth-startup-4473602938</t>
+    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Support Specialist</t>
@@ -499,6 +529,24 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -514,9 +562,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (37577)</t>
   </si>
   <si>
@@ -529,22 +574,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
+    <t xml:space="preserve">Network Operations &amp; Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
     <t xml:space="preserve">abra</t>
@@ -610,7 +649,7 @@
     <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4471735300</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4474046133</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Israel</t>
@@ -715,154 +754,145 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1017,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -995,7 +1025,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1011,7 +1041,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1093,7 +1123,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1109,7 +1139,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1151,7 +1181,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -1179,7 +1209,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1360,25 +1390,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3">
-        <v>88</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1386,31 +1416,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>84</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1418,19 +1448,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1442,7 +1472,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1450,31 +1480,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>74</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -1482,31 +1512,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -1514,31 +1544,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3">
+        <v>70</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="3">
-        <v>68</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1546,31 +1576,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="3">
-        <v>61</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1578,31 +1608,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="3">
+        <v>61</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>60</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="14">
@@ -1610,31 +1640,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1642,31 +1672,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1683,10 +1713,10 @@
         <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>122</v>
@@ -1706,31 +1736,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3">
+        <v>47</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>44</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18">
@@ -1744,25 +1774,25 @@
         <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -1770,31 +1800,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -1808,13 +1838,13 @@
         <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>141</v>
@@ -1826,7 +1856,7 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1840,25 +1870,25 @@
         <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F21" s="3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -1866,28 +1896,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
@@ -1898,31 +1928,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
@@ -1930,31 +1960,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -1971,10 +2001,10 @@
         <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>164</v>
@@ -1986,7 +2016,7 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
@@ -1994,31 +2024,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>27</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>24</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2057,7 +2087,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2136,7 +2166,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -2171,7 +2201,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2206,7 +2236,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -2241,7 +2271,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -2252,16 +2282,16 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3">
-        <v>88</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>176</v>
@@ -2270,33 +2300,33 @@
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>84</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>176</v>
@@ -2305,30 +2335,30 @@
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
@@ -2343,30 +2373,30 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="K8" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>80</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>74</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>176</v>
@@ -2375,33 +2405,33 @@
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>5</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>176</v>
@@ -2410,103 +2440,103 @@
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K10" s="3">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3">
+        <v>70</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="3">
-        <v>68</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="K11" s="3">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>68</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="3">
-        <v>61</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="K12" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3">
+        <v>61</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>60</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>176</v>
@@ -2515,33 +2545,33 @@
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>176</v>
@@ -2550,33 +2580,33 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="C15" s="3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>176</v>
@@ -2585,13 +2615,13 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="K15" s="3">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2605,10 +2635,10 @@
         <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>122</v>
@@ -2626,27 +2656,27 @@
         <v>124</v>
       </c>
       <c r="K16" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3">
+        <v>47</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>44</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>176</v>
@@ -2655,13 +2685,13 @@
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2672,16 +2702,16 @@
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>176</v>
@@ -2690,33 +2720,33 @@
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>176</v>
@@ -2725,13 +2755,13 @@
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2742,13 +2772,13 @@
         <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>141</v>
@@ -2763,10 +2793,10 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="K20" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2777,16 +2807,16 @@
         <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E21" s="3">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>176</v>
@@ -2795,33 +2825,33 @@
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K21" s="3">
-        <v>84</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>176</v>
@@ -2830,33 +2860,33 @@
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>176</v>
@@ -2865,33 +2895,33 @@
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="K23" s="3">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>126</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>176</v>
@@ -2900,13 +2930,13 @@
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
@@ -2920,10 +2950,10 @@
         <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>164</v>
@@ -2938,30 +2968,30 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>168</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>176</v>
@@ -2970,24 +3000,24 @@
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -2996,7 +3026,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>176</v>
@@ -3005,33 +3035,33 @@
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="K27" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>176</v>
@@ -3040,13 +3070,13 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="K28" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3057,51 +3087,51 @@
         <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>24</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="3">
-        <v>20</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>176</v>
@@ -3110,33 +3140,33 @@
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="3">
+        <v>23</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="3">
-        <v>12</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>176</v>
@@ -3145,13 +3175,13 @@
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K31" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -3162,66 +3192,66 @@
         <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="K32" s="3">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>205</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -3229,19 +3259,19 @@
         <v>208</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>58</v>
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>176</v>
@@ -3250,33 +3280,33 @@
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="K34" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>176</v>
@@ -3285,13 +3315,13 @@
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="K35" s="3">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -3305,13 +3335,13 @@
         <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>176</v>
@@ -3320,133 +3350,139 @@
         <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="K36" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="3">
+        <v>8</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="3">
-        <v>4</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>227</v>
+        <v>134</v>
       </c>
       <c r="K37" s="3">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>230</v>
+        <v>163</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>226</v>
+      </c>
       <c r="G38" s="3" t="s">
         <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K38" s="3">
-        <v>68</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="3">
+        <v>4</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
+      <c r="J39" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="K39" s="3">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>176</v>
       </c>
@@ -3454,17 +3490,83 @@
         <v>34</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="J40" s="3" t="s">
+      <c r="K40" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K40" s="3">
-        <v>61</v>
+      <c r="B41" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K41" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K42" s="3">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K40"/>
+  <autoFilter ref="A1:K42"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3505,6 +3607,8 @@
     <hyperlink ref="I38" r:id="rId37"/>
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3512,11 +3616,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="51" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="48" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3546,175 +3650,55 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>109</v>
+        <v>211</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>44</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3">
-        <v>44</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3">
-        <v>24</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G3"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
-    <hyperlink ref="F6" r:id="rId5"/>
-    <hyperlink ref="F7" r:id="rId6"/>
-    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3729,178 +3713,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="B9" s="3">
         <v>14</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3920,10 +3904,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2">
@@ -3931,10 +3915,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3">
@@ -3945,7 +3929,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
@@ -3953,10 +3937,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5">
@@ -3967,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
@@ -3978,7 +3962,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7">
@@ -3989,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4010,13 +3994,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2">
@@ -4027,7 +4011,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4036,10 +4020,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4051,7 +4035,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>234</v>
+        <v>292</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W41.xlsx
+++ b/reports/devops-juniors-israel-2026-W41.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-06T13:14:31</t>
+    <t xml:space="preserve">2026-10-07T13:12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,12 +103,12 @@
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -217,54 +217,42 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -310,6 +298,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
   </si>
   <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Operations Engineer</t>
   </si>
   <si>
@@ -358,276 +358,264 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator #1350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Docker, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%231350-at-rad-4473722167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voyantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4475569150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator (Monitoring Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-monitoring-team-at-jobgether-4471710321</t>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations &amp; Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-malamteam-4476555528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations &amp; Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
   </si>
   <si>
@@ -640,6 +628,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -670,13 +667,13 @@
     <t xml:space="preserve">Optimove</t>
   </si>
   <si>
-    <t xml:space="preserve">Dundee, Scotland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4978622101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-04</t>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
@@ -790,6 +787,9 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
@@ -799,9 +799,6 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -817,36 +814,36 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
@@ -877,10 +874,10 @@
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1025,7 +1022,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1033,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1041,7 +1038,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>376</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1123,7 +1120,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1131,7 +1128,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1139,7 +1136,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1155,7 +1152,7 @@
         <v>29</v>
       </c>
       <c r="B25" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1181,7 +1178,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -1189,7 +1186,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1209,7 +1206,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1297,7 +1294,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1390,25 +1387,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1416,31 +1413,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1448,19 +1445,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>81</v>
@@ -1472,7 +1469,7 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1480,31 +1477,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -1512,31 +1509,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -1544,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1559,16 +1556,16 @@
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1664,7 +1661,7 @@
         <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1684,7 +1681,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>117</v>
@@ -1696,7 +1693,7 @@
         <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
@@ -1707,28 +1704,28 @@
         <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="3">
+        <v>47</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>48</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -1736,19 +1733,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>126</v>
@@ -1774,25 +1771,25 @@
         <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3">
-        <v>46</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -1800,31 +1797,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3">
+        <v>39</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1832,31 +1829,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -1873,22 +1870,22 @@
         <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
@@ -1896,28 +1893,28 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>28</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3">
-        <v>39</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
@@ -1928,31 +1925,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="3">
+        <v>27</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>36</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -1960,19 +1957,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>159</v>
@@ -1984,7 +1981,7 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
@@ -1992,31 +1989,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26">
@@ -2024,31 +2021,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2084,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="43" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2101,7 +2098,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2116,22 +2113,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2154,7 +2151,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2166,7 +2163,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2180,7 +2177,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2189,7 +2186,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2201,7 +2198,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2224,7 +2221,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2236,7 +2233,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
@@ -2259,7 +2256,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2271,7 +2268,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -2282,89 +2279,89 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2373,91 +2370,91 @@
         <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K9" s="3">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K10" s="3">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2466,22 +2463,22 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="K11" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2504,7 +2501,7 @@
         <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>33</v>
@@ -2516,7 +2513,7 @@
         <v>103</v>
       </c>
       <c r="K12" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -2539,7 +2536,7 @@
         <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2551,7 +2548,7 @@
         <v>108</v>
       </c>
       <c r="K13" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -2574,7 +2571,7 @@
         <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2583,10 +2580,10 @@
         <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2603,13 +2600,13 @@
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2618,10 +2615,10 @@
         <v>118</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2629,57 +2626,57 @@
         <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3">
+        <v>47</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>48</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K16" s="3">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2691,7 +2688,7 @@
         <v>128</v>
       </c>
       <c r="K17" s="3">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -2702,101 +2699,101 @@
         <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>134</v>
+        <v>72</v>
       </c>
       <c r="K18" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3">
+        <v>39</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K20" s="3">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -2810,121 +2807,121 @@
         <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="K21" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>28</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <v>39</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>36</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>72</v>
       </c>
       <c r="K23" s="3">
-        <v>85</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -2933,91 +2930,91 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>161</v>
       </c>
       <c r="K24" s="3">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="K25" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="K26" s="3">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3026,33 +3023,33 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K27" s="3">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="C28" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3061,33 +3058,33 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="K28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3096,45 +3093,45 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="K29" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
@@ -3146,7 +3143,7 @@
         <v>193</v>
       </c>
       <c r="K30" s="3">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -3157,42 +3154,42 @@
         <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K31" s="3">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>135</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
@@ -3204,19 +3201,19 @@
         <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="K32" s="3">
-        <v>7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33">
@@ -3224,10 +3221,10 @@
         <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3236,33 +3233,33 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K33" s="3">
-        <v>53</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="C34" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3271,33 +3268,33 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3306,33 +3303,33 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="K35" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>27</v>
@@ -3341,27 +3338,27 @@
         <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="K36" s="3">
-        <v>2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>58</v>
@@ -3376,33 +3373,33 @@
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K37" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3411,33 +3408,33 @@
         <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="J38" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="K38" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>26</v>
@@ -3446,33 +3443,33 @@
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="J39" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="K39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3481,33 +3478,33 @@
         <v>4</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J40" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="K40" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -3517,30 +3514,30 @@
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J41" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="K41" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>26</v>
@@ -3550,19 +3547,19 @@
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J42" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>250</v>
-      </c>
       <c r="K42" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -3616,11 +3613,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3639,10 +3636,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3650,55 +3647,103 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>94</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>187</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>188</v>
+        <v>96</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>189</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>210</v>
+        <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>211</v>
+        <v>118</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>189</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3713,178 +3758,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="3">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="B3" s="3">
-        <v>25</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B7" s="3">
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8" s="3">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B8" s="3">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="3">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="B9" s="3">
-        <v>14</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B10" s="3">
         <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="3">
         <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B13" s="3">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="B13" s="3">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="3">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B14" s="3">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="3">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="B15" s="3">
-        <v>6</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B16" s="3">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>279</v>
-      </c>
-      <c r="B16" s="3">
-        <v>6</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3904,10 +3949,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="2">
@@ -3915,10 +3960,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3">
@@ -3926,10 +3971,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
@@ -3937,10 +3982,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5">
@@ -3951,7 +3996,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6">
@@ -3959,10 +4004,10 @@
         <v>29</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7">
@@ -3973,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3994,13 +4039,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="2">
@@ -4008,10 +4053,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4020,10 +4065,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4035,7 +4080,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W41.xlsx
+++ b/reports/devops-juniors-israel-2026-W41.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-07T13:12:55</t>
+    <t xml:space="preserve">2026-10-08T13:19:24</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -253,6 +253,24 @@
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior Technical Operations Engineer</t>
   </si>
   <si>
@@ -271,12 +289,6 @@
     <t xml:space="preserve">Security Analyst (Student Position)</t>
   </si>
   <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
   </si>
   <si>
@@ -358,6 +370,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
@@ -373,18 +400,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4476168349</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
   </si>
   <si>
@@ -403,6 +418,21 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineer Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Docker, Kubernetes, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8229871?gh_jid=8229871</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -502,6 +532,24 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -529,25 +577,7 @@
     <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4475562487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4477158844</t>
   </si>
   <si>
     <t xml:space="preserve">Network Operations &amp; Control</t>
@@ -562,15 +592,6 @@
     <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-malamteam-4476555528</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -628,15 +649,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -661,21 +673,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
   </si>
   <si>
@@ -781,13 +778,22 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
@@ -797,15 +803,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Bash/Shell</t>
@@ -1014,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1030,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1038,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -1120,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1128,7 +1125,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1136,7 +1133,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1144,7 +1141,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1178,7 +1175,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1206,7 +1203,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="43" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1451,25 +1448,25 @@
         <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1477,19 +1474,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>87</v>
@@ -1501,7 +1498,7 @@
         <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1509,31 +1506,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -1541,13 +1538,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1556,16 +1553,16 @@
         <v>70</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
@@ -1576,28 +1573,28 @@
         <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
+        <v>70</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>68</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -1605,31 +1602,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>68</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="3">
-        <v>61</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="14">
@@ -1637,31 +1634,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="3">
+        <v>61</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>60</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="15">
@@ -1669,31 +1666,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1701,31 +1698,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17">
@@ -1742,10 +1739,10 @@
         <v>125</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>126</v>
@@ -1757,7 +1754,7 @@
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18">
@@ -1765,19 +1762,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>131</v>
@@ -1789,7 +1786,7 @@
         <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1797,31 +1794,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -1829,31 +1826,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -1870,22 +1867,22 @@
         <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -1893,10 +1890,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>53</v>
@@ -1905,19 +1902,19 @@
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -1925,31 +1922,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -1957,19 +1954,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>159</v>
@@ -1981,7 +1978,7 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -1989,31 +1986,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="3">
+        <v>27</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F25" s="3">
-        <v>24</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -2021,31 +2018,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3">
+        <v>27</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="3">
-        <v>24</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2163,7 +2160,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -2198,7 +2195,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2233,7 +2230,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -2268,7 +2265,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -2303,7 +2300,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2338,7 +2335,7 @@
         <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -2349,16 +2346,16 @@
         <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>177</v>
@@ -2367,30 +2364,30 @@
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>87</v>
@@ -2405,30 +2402,30 @@
         <v>88</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3">
-        <v>7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>177</v>
@@ -2437,24 +2434,24 @@
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="K10" s="3">
-        <v>48</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2463,7 +2460,7 @@
         <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>177</v>
@@ -2472,13 +2469,13 @@
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -2486,89 +2483,89 @@
         <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3">
+        <v>70</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>68</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>68</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="3">
-        <v>61</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="K13" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3">
+        <v>61</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>60</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>177</v>
@@ -2577,33 +2574,33 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>177</v>
@@ -2612,33 +2609,33 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="C16" s="3" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>177</v>
@@ -2647,13 +2644,13 @@
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="K16" s="3">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2667,10 +2664,10 @@
         <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>126</v>
@@ -2685,27 +2682,27 @@
         <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="K17" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>131</v>
@@ -2720,65 +2717,65 @@
         <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="K18" s="3">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="K19" s="3">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>177</v>
@@ -2787,13 +2784,13 @@
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="K20" s="3">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2807,10 +2804,10 @@
         <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>146</v>
@@ -2819,24 +2816,24 @@
         <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>53</v>
@@ -2845,10 +2842,10 @@
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>177</v>
@@ -2857,65 +2854,65 @@
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>159</v>
@@ -2930,30 +2927,30 @@
         <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="3">
+        <v>27</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="3">
-        <v>24</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>177</v>
@@ -2962,33 +2959,33 @@
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="K25" s="3">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="3">
-        <v>24</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>177</v>
@@ -2997,13 +2994,13 @@
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K26" s="3">
-        <v>2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
@@ -3014,7 +3011,7 @@
         <v>179</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>116</v>
+        <v>180</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3023,7 +3020,7 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>177</v>
@@ -3032,24 +3029,24 @@
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K27" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3058,7 +3055,7 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>177</v>
@@ -3067,10 +3064,10 @@
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="K28" s="3">
         <v>0</v>
@@ -3078,10 +3075,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>125</v>
@@ -3093,7 +3090,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>177</v>
@@ -3102,33 +3099,33 @@
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>189</v>
+        <v>148</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>177</v>
@@ -3137,59 +3134,59 @@
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>196</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
@@ -3198,33 +3195,33 @@
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>54</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3233,7 +3230,7 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>177</v>
@@ -3242,24 +3239,24 @@
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>206</v>
+        <v>171</v>
       </c>
       <c r="K33" s="3">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3268,7 +3265,7 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>177</v>
@@ -3277,24 +3274,24 @@
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
@@ -3303,7 +3300,7 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>177</v>
@@ -3312,68 +3309,68 @@
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="K35" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>217</v>
+        <v>59</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="K36" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>58</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>177</v>
@@ -3382,129 +3379,127 @@
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>128</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K38" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
         <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K39" s="3">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>237</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K40" s="3">
-        <v>27</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>26</v>
@@ -3517,53 +3512,20 @@
         <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K41" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="K42" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K42"/>
+  <autoFilter ref="A1:K41"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3605,7 +3567,6 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3613,9 +3574,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="59" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3647,79 +3608,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
@@ -3728,13 +3689,13 @@
         <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3758,178 +3719,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="3">
+        <v>23</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="B2" s="3">
-        <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" s="3">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="B6" s="3">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="3">
+        <v>14</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="B9" s="3">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="3">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="3">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="B11" s="3">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B12" s="3">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="B12" s="3">
-        <v>9</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="3">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="B13" s="3">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B14" s="3">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="B14" s="3">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="3">
+        <v>7</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="B15" s="3">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3949,10 +3910,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2">
@@ -3960,10 +3921,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -3971,10 +3932,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -3982,10 +3943,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -3993,10 +3954,10 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -4007,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -4018,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4039,13 +4000,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="2">
@@ -4053,10 +4014,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4068,7 +4029,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4080,7 +4041,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W41.xlsx
+++ b/reports/devops-juniors-israel-2026-W41.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-08T13:19:24</t>
+    <t xml:space="preserve">2026-10-09T13:07:23</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,6 +217,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -250,9 +265,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -298,7 +310,7 @@
     <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+    <t xml:space="preserve">Amazon</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
@@ -307,7 +319,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
     <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
@@ -385,6 +397,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
   </si>
   <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">Network Operations Center</t>
   </si>
   <si>
@@ -418,21 +448,6 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Docker, Kubernetes, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8229871?gh_jid=8229871</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
   </si>
   <si>
@@ -514,7 +529,22 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">Fetcherr</t>
@@ -532,33 +562,12 @@
     <t xml:space="preserve">2026-08-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
     <t xml:space="preserve">evoke</t>
   </si>
   <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
   </si>
   <si>
@@ -649,6 +658,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -778,15 +796,15 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -823,22 +841,22 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
@@ -1011,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -1019,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1117,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1125,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1133,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1175,7 +1193,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
@@ -1183,7 +1201,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -1384,25 +1402,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="3">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="3">
-        <v>88</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1410,31 +1428,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3">
+        <v>88</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>84</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1442,31 +1460,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="3">
+        <v>84</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3">
-        <v>83</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1474,31 +1492,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="3">
+        <v>83</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="3">
-        <v>80</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -1506,19 +1524,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="3">
         <v>80</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3">
-        <v>74</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1530,7 +1548,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1538,31 +1556,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -1570,13 +1588,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="D12" s="3" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1585,16 +1603,16 @@
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -1605,28 +1623,28 @@
         <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="3">
-        <v>68</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1634,31 +1652,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="3">
+        <v>68</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="3">
-        <v>61</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1666,31 +1684,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="3">
+        <v>61</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>60</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1698,31 +1716,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>60</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="3">
-        <v>57</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -1730,31 +1748,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="3">
+        <v>57</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>48</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -1762,31 +1780,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>54</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3">
-        <v>46</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="19">
@@ -1794,31 +1812,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20">
@@ -1826,19 +1844,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>141</v>
@@ -1850,7 +1868,7 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
@@ -1858,19 +1876,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>146</v>
@@ -1882,7 +1900,7 @@
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -1896,25 +1914,25 @@
         <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -1928,25 +1946,25 @@
         <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>36</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3">
-        <v>34</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24">
@@ -1954,31 +1972,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1986,19 +2004,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>164</v>
@@ -2010,7 +2028,7 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26">
@@ -2027,7 +2045,7 @@
         <v>168</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3">
         <v>27</v>
@@ -2042,7 +2060,7 @@
         <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2113,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2110,22 +2128,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2148,7 +2166,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2160,7 +2178,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -2183,7 +2201,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2195,7 +2213,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2218,7 +2236,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2230,7 +2248,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -2253,7 +2271,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2265,7 +2283,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -2276,159 +2294,159 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3">
+        <v>100</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3">
-        <v>88</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>84</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3">
+        <v>84</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="3">
-        <v>83</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3">
+        <v>83</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>80</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="K9" s="3">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3">
         <v>80</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3">
-        <v>74</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2437,56 +2455,56 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K11" s="3">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="C12" s="3" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2495,22 +2513,22 @@
         <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -2518,171 +2536,171 @@
         <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3">
+        <v>70</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="3">
-        <v>68</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="K13" s="3">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>68</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="3">
-        <v>61</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="K14" s="3">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3">
+        <v>61</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>60</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="K15" s="3">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>60</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="3">
-        <v>57</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3">
+        <v>57</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="K17" s="3">
         <v>1</v>
@@ -2690,95 +2708,95 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>54</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3">
-        <v>46</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="K18" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>48</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>141</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
@@ -2787,33 +2805,33 @@
         <v>142</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="K20" s="3">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>146</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2822,10 +2840,10 @@
         <v>147</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="K21" s="3">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2836,31 +2854,31 @@
         <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>152</v>
+        <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -2871,89 +2889,89 @@
         <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>36</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="3">
-        <v>34</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="K23" s="3">
-        <v>1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K24" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2962,10 +2980,10 @@
         <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="K25" s="3">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -2979,7 +2997,7 @@
         <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E26" s="3">
         <v>27</v>
@@ -2988,7 +3006,7 @@
         <v>169</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
@@ -2997,56 +3015,56 @@
         <v>170</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="K26" s="3">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3">
+        <v>27</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>24</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>183</v>
-      </c>
       <c r="K27" s="3">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3055,33 +3073,33 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="C29" s="3" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3090,10 +3108,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3102,21 +3120,21 @@
         <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="K29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3125,103 +3143,103 @@
         <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="K30" s="3">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3">
+        <v>24</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="3">
-        <v>23</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="K31" s="3">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>53</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="K32" s="3">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3230,302 +3248,372 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K33" s="3">
-        <v>55</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="3">
+        <v>20</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>12</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="K34" s="3">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="3">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="J35" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E35" s="3">
-        <v>12</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="K35" s="3">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>8</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="K36" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="C37" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="K37" s="3">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>228</v>
+        <v>58</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>229</v>
+        <v>59</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>232</v>
+        <v>143</v>
       </c>
       <c r="K38" s="3">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="K39" s="3">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="K40" s="3">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K41" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K41" s="3">
-        <v>64</v>
+      <c r="J42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K42" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K43" s="3">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K43"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3567,6 +3655,8 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3574,9 +3664,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3597,10 +3687,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3608,103 +3698,31 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3">
-        <v>57</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3">
-        <v>44</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G2"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-    <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3719,178 +3737,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3910,10 +3928,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -3921,10 +3939,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -3932,10 +3950,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -3943,10 +3961,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -3957,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -3968,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
@@ -3979,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4000,13 +4018,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2">
@@ -4014,10 +4032,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4026,10 +4044,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4041,7 +4059,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W41.xlsx
+++ b/reports/devops-juniors-israel-2026-W41.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="291">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-09T13:07:23</t>
+    <t xml:space="preserve">2026-10-11T12:40:01</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -217,54 +217,60 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -367,21 +373,6 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logica-IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-logica-it-4473666027</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
   </si>
   <si>
@@ -529,6 +520,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
   </si>
   <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -547,21 +553,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -658,15 +649,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Analyst</t>
   </si>
   <si>
@@ -817,18 +799,18 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
@@ -841,6 +823,12 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -851,12 +839,6 @@
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">GCP</t>
@@ -1029,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -1053,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10">
@@ -1135,7 +1117,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1151,7 +1133,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1193,7 +1175,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -1402,25 +1384,25 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1428,13 +1410,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>28</v>
@@ -1443,16 +1425,16 @@
         <v>88</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1460,13 +1442,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1475,16 +1457,16 @@
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1492,13 +1474,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1507,16 +1489,16 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -1524,10 +1506,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>53</v>
@@ -1539,16 +1521,16 @@
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
@@ -1556,13 +1538,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1571,16 +1553,16 @@
         <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -1588,13 +1570,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1603,13 +1585,13 @@
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>62</v>
@@ -1620,7 +1602,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>58</v>
@@ -1635,16 +1617,16 @@
         <v>70</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
@@ -1652,13 +1634,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
@@ -1667,16 +1649,16 @@
         <v>68</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -1684,10 +1666,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>53</v>
@@ -1699,16 +1681,16 @@
         <v>61</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1716,31 +1698,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -1748,31 +1730,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1780,31 +1762,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19">
@@ -1812,31 +1794,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -1844,31 +1826,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -1876,31 +1858,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -1908,31 +1890,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -1940,31 +1922,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24">
@@ -1972,31 +1954,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>161</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25">
@@ -2004,31 +1986,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F25" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
@@ -2036,31 +2018,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
         <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2113,7 +2095,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2128,22 +2110,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2166,7 +2148,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2178,7 +2160,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2201,7 +2183,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2213,7 +2195,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -2236,7 +2218,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2248,7 +2230,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -2271,7 +2253,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2283,7 +2265,7 @@
         <v>62</v>
       </c>
       <c r="K5" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -2294,42 +2276,42 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>28</v>
@@ -2338,33 +2320,33 @@
         <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2373,33 +2355,33 @@
         <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2408,30 +2390,30 @@
         <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>53</v>
@@ -2443,33 +2425,33 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K10" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2478,33 +2460,33 @@
         <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2513,27 +2495,27 @@
         <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>62</v>
       </c>
       <c r="K12" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>58</v>
@@ -2548,33 +2530,33 @@
         <v>70</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K13" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
@@ -2583,30 +2565,30 @@
         <v>68</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K14" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>53</v>
@@ -2618,453 +2600,453 @@
         <v>61</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E16" s="3">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K16" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="K20" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K21" s="3">
-        <v>4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="K22" s="3">
-        <v>50</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="K23" s="3">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>53</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>161</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>162</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>62</v>
       </c>
       <c r="K24" s="3">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E25" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="K25" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
         <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>4</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" s="3">
+        <v>24</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27" s="3">
-        <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K27" s="3">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
@@ -3073,33 +3055,33 @@
         <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>186</v>
+        <v>90</v>
       </c>
       <c r="K28" s="3">
-        <v>37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3108,10 +3090,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3120,21 +3102,21 @@
         <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>88</v>
+        <v>191</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>150</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
@@ -3143,103 +3125,103 @@
         <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K32" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3248,372 +3230,302 @@
         <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="K33" s="3">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="K34" s="3">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
       <c r="K35" s="3">
-        <v>84</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>218</v>
+        <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>8</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="3">
-        <v>12</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="K36" s="3">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="K37" s="3">
-        <v>56</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="K38" s="3">
-        <v>44</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="K39" s="3">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="3">
-        <v>4</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>236</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K40" s="3">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E41" s="3">
-        <v>4</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>242</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K41" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="K42" s="3">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="K43" s="3">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K43"/>
+  <autoFilter ref="A1:K41"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3655,8 +3567,6 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3664,9 +3574,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3687,10 +3597,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3698,25 +3608,25 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3737,178 +3647,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3">
         <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B6" s="3">
         <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B7" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B9" s="3">
         <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B10" s="3">
         <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B14" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -3928,10 +3838,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2">
@@ -3939,10 +3849,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -3953,7 +3863,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -3961,10 +3871,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -3975,7 +3885,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -3986,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -3997,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4018,13 +3928,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
@@ -4035,7 +3945,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4044,10 +3954,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4059,7 +3969,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D4" s="3"/>
     </row>
